--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>退款单号</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>退货单号</t>
   </si>
@@ -56,6 +53,21 @@
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>174321199590464428234</t>
+  </si>
+  <si>
+    <t>淘宝</t>
+  </si>
+  <si>
+    <t>天猫-优篮子旗舰店</t>
+  </si>
+  <si>
+    <t>rwer</t>
+  </si>
+  <si>
+    <t>作废</t>
   </si>
 </sst>
 </file>
@@ -700,11 +712,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1026,10 +1044,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="11" max="12" width="9.375"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:14">
+    <row r="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,17 +1084,74 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>324234</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>34</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2">
+        <v>44562</v>
+      </c>
+      <c r="L2" s="2">
+        <v>40548</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576 L2:L1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>退货单号</t>
   </si>
@@ -53,21 +53,6 @@
   </si>
   <si>
     <t>错误信息</t>
-  </si>
-  <si>
-    <t>174321199590464428234</t>
-  </si>
-  <si>
-    <t>淘宝</t>
-  </si>
-  <si>
-    <t>天猫-优篮子旗舰店</t>
-  </si>
-  <si>
-    <t>rwer</t>
-  </si>
-  <si>
-    <t>作废</t>
   </si>
 </sst>
 </file>
@@ -720,9 +705,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1091,43 +1073,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
-        <v>324234</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>34</v>
-      </c>
-      <c r="G2">
-        <v>34</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2">
-        <v>44562</v>
-      </c>
-      <c r="L2" s="2">
-        <v>40548</v>
-      </c>
+    <row r="2" spans="11:12">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
@@ -16,25 +16,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>退货单号</t>
-  </si>
-  <si>
-    <t>原订单号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>退货数量</t>
-  </si>
-  <si>
-    <t>退货金额</t>
+    <t>*退货单号</t>
+  </si>
+  <si>
+    <t>*原订单号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*退货数量</t>
+  </si>
+  <si>
+    <t>*退货金额</t>
   </si>
   <si>
     <t>汇率</t>
@@ -43,13 +43,13 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>退货状态</t>
-  </si>
-  <si>
-    <t>退货时间</t>
-  </si>
-  <si>
-    <t>原订单时间</t>
+    <t>*退货状态</t>
+  </si>
+  <si>
+    <t>*退货时间</t>
+  </si>
+  <si>
+    <t>*币种</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -1066,10 +1066,10 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       <c r="L2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
@@ -1091,7 +1091,7 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576 L2:L1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
@@ -1099,6 +1099,9 @@
       <formula1>0</formula1>
       <formula2>9999999999999990</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"待处理,已退款,已重发,已完成,已作废"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpReturnOrderInfoTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>*退货单号</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>*币种</t>
-  </si>
-  <si>
-    <t>错误信息</t>
   </si>
 </sst>
 </file>
@@ -1026,13 +1023,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="11" max="12" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:13">
+    <row r="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,9 +1066,6 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2" spans="11:12">
       <c r="K2" s="2"/>
@@ -1082,6 +1076,9 @@
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"待处理,已退款,已重发,已完成,已作废"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>0</formula1>
@@ -1099,9 +1096,6 @@
       <formula1>0</formula1>
       <formula2>9999999999999990</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>"待处理,已退款,已重发,已完成,已作废"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
